--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.77114870989177</v>
+        <v>4.837811665357413</v>
       </c>
       <c r="D2" t="n">
-        <v>30.30211490756691</v>
+        <v>4.924093672479622</v>
       </c>
       <c r="E2" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F2" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.55737528473523</v>
+        <v>6.103073483769475</v>
       </c>
       <c r="D3" t="n">
-        <v>37.4259199254653</v>
+        <v>6.081711987888112</v>
       </c>
       <c r="E3" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F3" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.05226250447932</v>
+        <v>5.85849265697789</v>
       </c>
       <c r="D4" t="n">
-        <v>35.69158521147682</v>
+        <v>5.799882596864983</v>
       </c>
       <c r="E4" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F4" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.00839420009919</v>
+        <v>4.876364057516119</v>
       </c>
       <c r="D5" t="n">
-        <v>29.92577335058564</v>
+        <v>4.862938169470167</v>
       </c>
       <c r="E5" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F5" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.91230775173988</v>
+        <v>3.23575000965773</v>
       </c>
       <c r="D6" t="n">
-        <v>57.13587534263613</v>
+        <v>9.284579743178371</v>
       </c>
       <c r="E6" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F6" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.55397531527947</v>
+        <v>3.015020988732914</v>
       </c>
       <c r="D7" t="n">
-        <v>53.08294674164024</v>
+        <v>8.625978845516538</v>
       </c>
       <c r="E7" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F7" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.32464745020429</v>
+        <v>3.302755210658197</v>
       </c>
       <c r="D8" t="n">
-        <v>20.41914256719928</v>
+        <v>3.318110667169883</v>
       </c>
       <c r="E8" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.66984258222674</v>
+        <v>7.908849419611845</v>
       </c>
       <c r="D9" t="n">
-        <v>48.80394107441105</v>
+        <v>7.930640424591796</v>
       </c>
       <c r="E9" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F9" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.88157036839038</v>
+        <v>6.643255184863436</v>
       </c>
       <c r="D10" t="n">
-        <v>41.24069321568003</v>
+        <v>6.701612647548005</v>
       </c>
       <c r="E10" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F10" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.6351919242006</v>
+        <v>9.853218687682599</v>
       </c>
       <c r="D11" t="n">
-        <v>60.76866211047435</v>
+        <v>9.874907592952082</v>
       </c>
       <c r="E11" t="n">
-        <v>12.830332909395</v>
+        <v>2.084929097776687</v>
       </c>
       <c r="F11" t="n">
-        <v>12.4797073954076</v>
+        <v>2.027952451753734</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
